--- a/Excel/StartConfig/Google/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -91,31 +91,16 @@
     <t>mongodb://localhost:27017/</t>
   </si>
   <si>
-    <t>WJBH1</t>
-  </si>
-  <si>
-    <t>WJBH2</t>
-  </si>
-  <si>
-    <t>封测区</t>
-  </si>
-  <si>
-    <t>WJBH3</t>
-  </si>
-  <si>
-    <t>WJBH4</t>
-  </si>
-  <si>
-    <t>WJBH5</t>
-  </si>
-  <si>
-    <t>WJBH202(center)</t>
+    <t>WJBeta171</t>
+  </si>
+  <si>
+    <t>WJBeta202(center)</t>
   </si>
   <si>
     <t>#中心服</t>
   </si>
   <si>
-    <t>WJBH203(robot)</t>
+    <t>WJBeta203(robot)</t>
   </si>
   <si>
     <t>#机器人</t>
@@ -131,7 +116,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +138,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -297,12 +288,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -632,141 +623,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -777,6 +765,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1125,177 +1114,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:G12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="C3:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="41.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="33.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="23.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="23.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:6">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="3:6">
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="3:6">
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="3:6">
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
+    <row r="6" spans="3:7">
+      <c r="C6" s="2">
+        <v>171</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="4">
+        <v>171</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="3:7">
-      <c r="C7" s="3">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="2">
+        <v>202</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="5">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="4">
+        <v>202</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="3:7">
-      <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="2">
+        <v>203</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="5">
-        <v>3</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="E8" s="4">
+        <v>203</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="3:7">
-      <c r="C9" s="3">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="5">
-        <v>3</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="G8" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="3:7">
-      <c r="C10" s="3">
-        <v>5</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="5">
-        <v>5</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="3:7">
-      <c r="C11" s="3">
-        <v>202</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="5">
-        <v>202</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="3:7">
-      <c r="C12" s="3">
-        <v>203</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="5">
-        <v>203</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Google/StartZoneConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartZoneConfig@s.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>WJBeta171</t>
+  </si>
+  <si>
+    <t>ValorArena</t>
   </si>
   <si>
     <t>WJBeta202(center)</t>
@@ -1184,7 +1187,9 @@
       <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="3:7">
       <c r="C7" s="2">
@@ -1197,10 +1202,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="3:7">
@@ -1214,10 +1219,10 @@
         <v>203</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
